--- a/datasets/pco/04 Participación gamificación sintética.xlsx
+++ b/datasets/pco/04 Participación gamificación sintética.xlsx
@@ -3381,7 +3381,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>DATOS 100 % FICTICIOS para el programa IA-abilities (Coknow). No corresponden a la Compañía ni a ninguna persona real.</t>
+          <t>DATOS 100 % FICTICIOS para el programa IA-abilities. No corresponden a la Compañía ni a ninguna persona real.</t>
         </is>
       </c>
     </row>

--- a/datasets/pco/04 Participación gamificación sintética.xlsx
+++ b/datasets/pco/04 Participación gamificación sintética.xlsx
@@ -3372,7 +3372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -3395,13 +3395,6 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Tendencias sembradas: Tecnología y Servicio al cliente caen semana a semana; Talento Humano sube.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
           <t>Uso sugerido (nivel 02, mesa de talento, y demo del nivel 04): informe de participación de una página, qué reto funciona mejor y qué áreas necesitan acción; luego un tablero HTML que se actualiza al cargar la semana nueva.</t>
         </is>
       </c>
